--- a/astro-site/public/dl/restaurant-financial-plan-templates/01-restaurant-financial-projections-3-year.xlsx
+++ b/astro-site/public/dl/restaurant-financial-plan-templates/01-restaurant-financial-projections-3-year.xlsx
@@ -163,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -221,6 +221,9 @@
     <xf numFmtId="166" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="8" fillId="3" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
@@ -231,6 +234,9 @@
     <xf numFmtId="4" fontId="8" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -788,7 +794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B27"/>
+  <dimension ref="A2:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -914,6 +920,13 @@
       <c r="B27" s="18" t="inlineStr">
         <is>
           <t>Version 2.0 · October 2026 · aichef.pro/en/digital-products/restaurant-financial-plan-templates · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="27" t="inlineStr">
+        <is>
+          <t>Planning tool, not financial, tax or legal advice. Requirements vary by state and city — check with your accountant and local authorities.</t>
         </is>
       </c>
     </row>
@@ -1057,43 +1070,43 @@
           <t>Dine-in (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="28">
+      <c r="B6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="29">
         <f>SUM(B6:M6)</f>
         <v>0.0</v>
       </c>
@@ -1104,43 +1117,43 @@
           <t>Bar (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="28">
+      <c r="B7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="29">
         <f>SUM(B7:M7)</f>
         <v>0.0</v>
       </c>
@@ -1151,43 +1164,43 @@
           <t>Delivery (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="28">
+      <c r="B8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="29">
         <f>SUM(B8:M8)</f>
         <v>0.0</v>
       </c>
@@ -1198,43 +1211,43 @@
           <t>Events / Catering (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="28">
+      <c r="B9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="29">
         <f>SUM(B9:M9)</f>
         <v>0.0</v>
       </c>
@@ -1245,55 +1258,55 @@
           <t>TOTAL REVENUE (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="29">
         <f>SUM(B6:B9)</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>SUM(C6:C9)</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>SUM(D6:D9)</f>
         <v>0.0</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>SUM(E6:E9)</f>
         <v>0.0</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f>SUM(F6:F9)</f>
         <v>0.0</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="29">
         <f>SUM(G6:G9)</f>
         <v>0.0</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="29">
         <f>SUM(H6:H9)</f>
         <v>0.0</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="29">
         <f>SUM(I6:I9)</f>
         <v>0.0</v>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="29">
         <f>SUM(J6:J9)</f>
         <v>0.0</v>
       </c>
-      <c r="K10" s="28">
+      <c r="K10" s="29">
         <f>SUM(K6:K9)</f>
         <v>0.0</v>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="29">
         <f>SUM(L6:L9)</f>
         <v>0.0</v>
       </c>
-      <c r="M10" s="28">
+      <c r="M10" s="29">
         <f>SUM(M6:M9)</f>
         <v>0.0</v>
       </c>
-      <c r="N10" s="28">
+      <c r="N10" s="29">
         <f>SUM(N6:N9)</f>
         <v>0.0</v>
       </c>
@@ -1311,43 +1324,43 @@
           <t>Food cost (raw materials)</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="28">
+      <c r="B13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="29">
         <f>SUM(B13:M13)</f>
         <v>0.0</v>
       </c>
@@ -1358,43 +1371,43 @@
           <t>Beverage cost (bar)</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="28">
+      <c r="B14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="29">
         <f>SUM(B14:M14)</f>
         <v>0.0</v>
       </c>
@@ -1405,43 +1418,43 @@
           <t>Labor</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="28">
+      <c r="B15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="29">
         <f>SUM(B15:M15)</f>
         <v>0.0</v>
       </c>
@@ -1452,55 +1465,55 @@
           <t>Delivery platform fees</t>
         </is>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="29">
         <f>B8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <f>C8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <f>D8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <f>E8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f>F8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="29">
         <f>G8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="29">
         <f>H8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="29">
         <f>I8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="J16" s="28">
+      <c r="J16" s="29">
         <f>J8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="K16" s="28">
+      <c r="K16" s="29">
         <f>K8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="L16" s="28">
+      <c r="L16" s="29">
         <f>L8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="M16" s="28">
+      <c r="M16" s="29">
         <f>M8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="N16" s="28">
+      <c r="N16" s="29">
         <f>SUM(B16:M16)</f>
         <v>0.0</v>
       </c>
@@ -1511,43 +1524,43 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="28">
+      <c r="B17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="29">
         <f>SUM(B17:M17)</f>
         <v>0.0</v>
       </c>
@@ -1558,43 +1571,43 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="28">
+      <c r="B18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="29">
         <f>SUM(B18:M18)</f>
         <v>0.0</v>
       </c>
@@ -1605,43 +1618,43 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="28">
+      <c r="B19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="29">
         <f>SUM(B19:M19)</f>
         <v>0.0</v>
       </c>
@@ -1652,43 +1665,43 @@
           <t>Admin / Other</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="28">
+      <c r="B20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="29">
         <f>SUM(B20:M20)</f>
         <v>0.0</v>
       </c>
@@ -1699,55 +1712,55 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="29">
         <f>SUM(B13:B20)</f>
         <v>0.0</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="29">
         <f>SUM(C13:C20)</f>
         <v>0.0</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="29">
         <f>SUM(D13:D20)</f>
         <v>0.0</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="29">
         <f>SUM(E13:E20)</f>
         <v>0.0</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="29">
         <f>SUM(F13:F20)</f>
         <v>0.0</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="29">
         <f>SUM(G13:G20)</f>
         <v>0.0</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="29">
         <f>SUM(H13:H20)</f>
         <v>0.0</v>
       </c>
-      <c r="I21" s="28">
+      <c r="I21" s="29">
         <f>SUM(I13:I20)</f>
         <v>0.0</v>
       </c>
-      <c r="J21" s="28">
+      <c r="J21" s="29">
         <f>SUM(J13:J20)</f>
         <v>0.0</v>
       </c>
-      <c r="K21" s="28">
+      <c r="K21" s="29">
         <f>SUM(K13:K20)</f>
         <v>0.0</v>
       </c>
-      <c r="L21" s="28">
+      <c r="L21" s="29">
         <f>SUM(L13:L20)</f>
         <v>0.0</v>
       </c>
-      <c r="M21" s="28">
+      <c r="M21" s="29">
         <f>SUM(M13:M20)</f>
         <v>0.0</v>
       </c>
-      <c r="N21" s="28">
+      <c r="N21" s="29">
         <f>SUM(N13:N20)</f>
         <v>0.0</v>
       </c>
@@ -1774,55 +1787,55 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="29">
         <f>B10-B21</f>
         <v>0.0</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="29">
         <f>C10-C21</f>
         <v>0.0</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="29">
         <f>D10-D21</f>
         <v>0.0</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="29">
         <f>E10-E21</f>
         <v>0.0</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="29">
         <f>F10-F21</f>
         <v>0.0</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="29">
         <f>G10-G21</f>
         <v>0.0</v>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="29">
         <f>H10-H21</f>
         <v>0.0</v>
       </c>
-      <c r="I23" s="28">
+      <c r="I23" s="29">
         <f>I10-I21</f>
         <v>0.0</v>
       </c>
-      <c r="J23" s="28">
+      <c r="J23" s="29">
         <f>J10-J21</f>
         <v>0.0</v>
       </c>
-      <c r="K23" s="28">
+      <c r="K23" s="29">
         <f>K10-K21</f>
         <v>0.0</v>
       </c>
-      <c r="L23" s="28">
+      <c r="L23" s="29">
         <f>L10-L21</f>
         <v>0.0</v>
       </c>
-      <c r="M23" s="28">
+      <c r="M23" s="29">
         <f>M10-M21</f>
         <v>0.0</v>
       </c>
-      <c r="N23" s="28">
+      <c r="N23" s="29">
         <f>N10-N21</f>
         <v>0.0</v>
       </c>
@@ -1893,8 +1906,8 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>Delivery platform fee % (on the delivery sales in row 8)</t>
         </is>
@@ -2070,43 +2083,43 @@
           <t>Dine-in (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="28">
+      <c r="B6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="29">
         <f>SUM(B6:M6)</f>
         <v>0.0</v>
       </c>
@@ -2117,43 +2130,43 @@
           <t>Bar (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="28">
+      <c r="B7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="29">
         <f>SUM(B7:M7)</f>
         <v>0.0</v>
       </c>
@@ -2164,43 +2177,43 @@
           <t>Delivery (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="28">
+      <c r="B8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="29">
         <f>SUM(B8:M8)</f>
         <v>0.0</v>
       </c>
@@ -2211,43 +2224,43 @@
           <t>Events / Catering (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="28">
+      <c r="B9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="29">
         <f>SUM(B9:M9)</f>
         <v>0.0</v>
       </c>
@@ -2258,55 +2271,55 @@
           <t>TOTAL REVENUE (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="29">
         <f>SUM(B6:B9)</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>SUM(C6:C9)</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>SUM(D6:D9)</f>
         <v>0.0</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>SUM(E6:E9)</f>
         <v>0.0</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f>SUM(F6:F9)</f>
         <v>0.0</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="29">
         <f>SUM(G6:G9)</f>
         <v>0.0</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="29">
         <f>SUM(H6:H9)</f>
         <v>0.0</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="29">
         <f>SUM(I6:I9)</f>
         <v>0.0</v>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="29">
         <f>SUM(J6:J9)</f>
         <v>0.0</v>
       </c>
-      <c r="K10" s="28">
+      <c r="K10" s="29">
         <f>SUM(K6:K9)</f>
         <v>0.0</v>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="29">
         <f>SUM(L6:L9)</f>
         <v>0.0</v>
       </c>
-      <c r="M10" s="28">
+      <c r="M10" s="29">
         <f>SUM(M6:M9)</f>
         <v>0.0</v>
       </c>
-      <c r="N10" s="28">
+      <c r="N10" s="29">
         <f>SUM(N6:N9)</f>
         <v>0.0</v>
       </c>
@@ -2324,43 +2337,43 @@
           <t>Food cost (raw materials)</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="28">
+      <c r="B13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="29">
         <f>SUM(B13:M13)</f>
         <v>0.0</v>
       </c>
@@ -2371,43 +2384,43 @@
           <t>Beverage cost (bar)</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="28">
+      <c r="B14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="29">
         <f>SUM(B14:M14)</f>
         <v>0.0</v>
       </c>
@@ -2418,43 +2431,43 @@
           <t>Labor</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="28">
+      <c r="B15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="29">
         <f>SUM(B15:M15)</f>
         <v>0.0</v>
       </c>
@@ -2465,55 +2478,55 @@
           <t>Delivery platform fees</t>
         </is>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="29">
         <f>B8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <f>C8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <f>D8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <f>E8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f>F8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="29">
         <f>G8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="29">
         <f>H8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="29">
         <f>I8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="J16" s="28">
+      <c r="J16" s="29">
         <f>J8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="K16" s="28">
+      <c r="K16" s="29">
         <f>K8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="L16" s="28">
+      <c r="L16" s="29">
         <f>L8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="M16" s="28">
+      <c r="M16" s="29">
         <f>M8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="N16" s="28">
+      <c r="N16" s="29">
         <f>SUM(B16:M16)</f>
         <v>0.0</v>
       </c>
@@ -2524,43 +2537,43 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="28">
+      <c r="B17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="29">
         <f>SUM(B17:M17)</f>
         <v>0.0</v>
       </c>
@@ -2571,43 +2584,43 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="28">
+      <c r="B18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="29">
         <f>SUM(B18:M18)</f>
         <v>0.0</v>
       </c>
@@ -2618,43 +2631,43 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="28">
+      <c r="B19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="29">
         <f>SUM(B19:M19)</f>
         <v>0.0</v>
       </c>
@@ -2665,43 +2678,43 @@
           <t>Admin / Other</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="28">
+      <c r="B20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="29">
         <f>SUM(B20:M20)</f>
         <v>0.0</v>
       </c>
@@ -2712,55 +2725,55 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="29">
         <f>SUM(B13:B20)</f>
         <v>0.0</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="29">
         <f>SUM(C13:C20)</f>
         <v>0.0</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="29">
         <f>SUM(D13:D20)</f>
         <v>0.0</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="29">
         <f>SUM(E13:E20)</f>
         <v>0.0</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="29">
         <f>SUM(F13:F20)</f>
         <v>0.0</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="29">
         <f>SUM(G13:G20)</f>
         <v>0.0</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="29">
         <f>SUM(H13:H20)</f>
         <v>0.0</v>
       </c>
-      <c r="I21" s="28">
+      <c r="I21" s="29">
         <f>SUM(I13:I20)</f>
         <v>0.0</v>
       </c>
-      <c r="J21" s="28">
+      <c r="J21" s="29">
         <f>SUM(J13:J20)</f>
         <v>0.0</v>
       </c>
-      <c r="K21" s="28">
+      <c r="K21" s="29">
         <f>SUM(K13:K20)</f>
         <v>0.0</v>
       </c>
-      <c r="L21" s="28">
+      <c r="L21" s="29">
         <f>SUM(L13:L20)</f>
         <v>0.0</v>
       </c>
-      <c r="M21" s="28">
+      <c r="M21" s="29">
         <f>SUM(M13:M20)</f>
         <v>0.0</v>
       </c>
-      <c r="N21" s="28">
+      <c r="N21" s="29">
         <f>SUM(N13:N20)</f>
         <v>0.0</v>
       </c>
@@ -2787,55 +2800,55 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="29">
         <f>B10-B21</f>
         <v>0.0</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="29">
         <f>C10-C21</f>
         <v>0.0</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="29">
         <f>D10-D21</f>
         <v>0.0</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="29">
         <f>E10-E21</f>
         <v>0.0</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="29">
         <f>F10-F21</f>
         <v>0.0</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="29">
         <f>G10-G21</f>
         <v>0.0</v>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="29">
         <f>H10-H21</f>
         <v>0.0</v>
       </c>
-      <c r="I23" s="28">
+      <c r="I23" s="29">
         <f>I10-I21</f>
         <v>0.0</v>
       </c>
-      <c r="J23" s="28">
+      <c r="J23" s="29">
         <f>J10-J21</f>
         <v>0.0</v>
       </c>
-      <c r="K23" s="28">
+      <c r="K23" s="29">
         <f>K10-K21</f>
         <v>0.0</v>
       </c>
-      <c r="L23" s="28">
+      <c r="L23" s="29">
         <f>L10-L21</f>
         <v>0.0</v>
       </c>
-      <c r="M23" s="28">
+      <c r="M23" s="29">
         <f>M10-M21</f>
         <v>0.0</v>
       </c>
-      <c r="N23" s="28">
+      <c r="N23" s="29">
         <f>N10-N21</f>
         <v>0.0</v>
       </c>
@@ -2906,8 +2919,8 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>Delivery platform fee % (on the delivery sales in row 8)</t>
         </is>
@@ -3083,43 +3096,43 @@
           <t>Dine-in (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="28">
+      <c r="B6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="29">
         <f>SUM(B6:M6)</f>
         <v>0.0</v>
       </c>
@@ -3130,43 +3143,43 @@
           <t>Bar (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="28">
+      <c r="B7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="29">
         <f>SUM(B7:M7)</f>
         <v>0.0</v>
       </c>
@@ -3177,43 +3190,43 @@
           <t>Delivery (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="28">
+      <c r="B8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="29">
         <f>SUM(B8:M8)</f>
         <v>0.0</v>
       </c>
@@ -3224,43 +3237,43 @@
           <t>Events / Catering (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="28">
+      <c r="B9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="29">
         <f>SUM(B9:M9)</f>
         <v>0.0</v>
       </c>
@@ -3271,55 +3284,55 @@
           <t>TOTAL REVENUE (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="29">
         <f>SUM(B6:B9)</f>
         <v>0.0</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>SUM(C6:C9)</f>
         <v>0.0</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>SUM(D6:D9)</f>
         <v>0.0</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>SUM(E6:E9)</f>
         <v>0.0</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f>SUM(F6:F9)</f>
         <v>0.0</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="29">
         <f>SUM(G6:G9)</f>
         <v>0.0</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="29">
         <f>SUM(H6:H9)</f>
         <v>0.0</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="29">
         <f>SUM(I6:I9)</f>
         <v>0.0</v>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="29">
         <f>SUM(J6:J9)</f>
         <v>0.0</v>
       </c>
-      <c r="K10" s="28">
+      <c r="K10" s="29">
         <f>SUM(K6:K9)</f>
         <v>0.0</v>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="29">
         <f>SUM(L6:L9)</f>
         <v>0.0</v>
       </c>
-      <c r="M10" s="28">
+      <c r="M10" s="29">
         <f>SUM(M6:M9)</f>
         <v>0.0</v>
       </c>
-      <c r="N10" s="28">
+      <c r="N10" s="29">
         <f>SUM(N6:N9)</f>
         <v>0.0</v>
       </c>
@@ -3337,43 +3350,43 @@
           <t>Food cost (raw materials)</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="28">
+      <c r="B13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="29">
         <f>SUM(B13:M13)</f>
         <v>0.0</v>
       </c>
@@ -3384,43 +3397,43 @@
           <t>Beverage cost (bar)</t>
         </is>
       </c>
-      <c r="B14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="28">
+      <c r="B14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="29">
         <f>SUM(B14:M14)</f>
         <v>0.0</v>
       </c>
@@ -3431,43 +3444,43 @@
           <t>Labor</t>
         </is>
       </c>
-      <c r="B15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="28">
+      <c r="B15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="29">
         <f>SUM(B15:M15)</f>
         <v>0.0</v>
       </c>
@@ -3478,55 +3491,55 @@
           <t>Delivery platform fees</t>
         </is>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="29">
         <f>B8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <f>C8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <f>D8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <f>E8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f>F8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="29">
         <f>G8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="29">
         <f>H8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="29">
         <f>I8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="J16" s="28">
+      <c r="J16" s="29">
         <f>J8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="K16" s="28">
+      <c r="K16" s="29">
         <f>K8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="L16" s="28">
+      <c r="L16" s="29">
         <f>L8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="M16" s="28">
+      <c r="M16" s="29">
         <f>M8*$B$27</f>
         <v>0.0</v>
       </c>
-      <c r="N16" s="28">
+      <c r="N16" s="29">
         <f>SUM(B16:M16)</f>
         <v>0.0</v>
       </c>
@@ -3537,43 +3550,43 @@
           <t>Rent</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="28">
+      <c r="B17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="29">
         <f>SUM(B17:M17)</f>
         <v>0.0</v>
       </c>
@@ -3584,43 +3597,43 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="28">
+      <c r="B18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="29">
         <f>SUM(B18:M18)</f>
         <v>0.0</v>
       </c>
@@ -3631,43 +3644,43 @@
           <t>Marketing</t>
         </is>
       </c>
-      <c r="B19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="28">
+      <c r="B19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="29">
         <f>SUM(B19:M19)</f>
         <v>0.0</v>
       </c>
@@ -3678,43 +3691,43 @@
           <t>Admin / Other</t>
         </is>
       </c>
-      <c r="B20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="28">
+      <c r="B20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="29">
         <f>SUM(B20:M20)</f>
         <v>0.0</v>
       </c>
@@ -3725,55 +3738,55 @@
           <t>TOTAL EXPENSES</t>
         </is>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="29">
         <f>SUM(B13:B20)</f>
         <v>0.0</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="29">
         <f>SUM(C13:C20)</f>
         <v>0.0</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="29">
         <f>SUM(D13:D20)</f>
         <v>0.0</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="29">
         <f>SUM(E13:E20)</f>
         <v>0.0</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="29">
         <f>SUM(F13:F20)</f>
         <v>0.0</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="29">
         <f>SUM(G13:G20)</f>
         <v>0.0</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="29">
         <f>SUM(H13:H20)</f>
         <v>0.0</v>
       </c>
-      <c r="I21" s="28">
+      <c r="I21" s="29">
         <f>SUM(I13:I20)</f>
         <v>0.0</v>
       </c>
-      <c r="J21" s="28">
+      <c r="J21" s="29">
         <f>SUM(J13:J20)</f>
         <v>0.0</v>
       </c>
-      <c r="K21" s="28">
+      <c r="K21" s="29">
         <f>SUM(K13:K20)</f>
         <v>0.0</v>
       </c>
-      <c r="L21" s="28">
+      <c r="L21" s="29">
         <f>SUM(L13:L20)</f>
         <v>0.0</v>
       </c>
-      <c r="M21" s="28">
+      <c r="M21" s="29">
         <f>SUM(M13:M20)</f>
         <v>0.0</v>
       </c>
-      <c r="N21" s="28">
+      <c r="N21" s="29">
         <f>SUM(N13:N20)</f>
         <v>0.0</v>
       </c>
@@ -3800,55 +3813,55 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="29">
         <f>B10-B21</f>
         <v>0.0</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="29">
         <f>C10-C21</f>
         <v>0.0</v>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="29">
         <f>D10-D21</f>
         <v>0.0</v>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="29">
         <f>E10-E21</f>
         <v>0.0</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="29">
         <f>F10-F21</f>
         <v>0.0</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="29">
         <f>G10-G21</f>
         <v>0.0</v>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="29">
         <f>H10-H21</f>
         <v>0.0</v>
       </c>
-      <c r="I23" s="28">
+      <c r="I23" s="29">
         <f>I10-I21</f>
         <v>0.0</v>
       </c>
-      <c r="J23" s="28">
+      <c r="J23" s="29">
         <f>J10-J21</f>
         <v>0.0</v>
       </c>
-      <c r="K23" s="28">
+      <c r="K23" s="29">
         <f>K10-K21</f>
         <v>0.0</v>
       </c>
-      <c r="L23" s="28">
+      <c r="L23" s="29">
         <f>L10-L21</f>
         <v>0.0</v>
       </c>
-      <c r="M23" s="28">
+      <c r="M23" s="29">
         <f>M10-M21</f>
         <v>0.0</v>
       </c>
-      <c r="N23" s="28">
+      <c r="N23" s="29">
         <f>N10-N21</f>
         <v>0.0</v>
       </c>
@@ -3919,8 +3932,8 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t>Delivery platform fee % (on the delivery sales in row 8)</t>
         </is>
@@ -4035,15 +4048,15 @@
           <t>Total Revenue (excl. sales tax)</t>
         </is>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="32">
         <f>'Year 1'!N10</f>
         <v>0.0</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="32">
         <f>'Year 2'!N10</f>
         <v>0.0</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="32">
         <f>'Year 3'!N10</f>
         <v>0.0</v>
       </c>
@@ -4058,15 +4071,15 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="32">
         <f>'Year 1'!N21</f>
         <v>0.0</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="32">
         <f>'Year 2'!N21</f>
         <v>0.0</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="32">
         <f>'Year 3'!N21</f>
         <v>0.0</v>
       </c>
@@ -4081,15 +4094,15 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="32">
         <f>'Year 1'!N23</f>
         <v>0.0</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="32">
         <f>'Year 2'!N23</f>
         <v>0.0</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="32">
         <f>'Year 3'!N23</f>
         <v>0.0</v>
       </c>
